--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132706115</v>
+        <v>132706099</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484521</v>
+        <v>484145</v>
       </c>
       <c r="R7" t="n">
-        <v>7084338</v>
+        <v>7084092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706099</v>
+        <v>132706115</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484145</v>
+        <v>484521</v>
       </c>
       <c r="R8" t="n">
-        <v>7084092</v>
+        <v>7084338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132706116</v>
+        <v>132706135</v>
       </c>
       <c r="B3" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484434</v>
+        <v>484208</v>
       </c>
       <c r="R3" t="n">
-        <v>7084114</v>
+        <v>7084096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706135</v>
+        <v>132706116</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484208</v>
+        <v>484434</v>
       </c>
       <c r="R4" t="n">
-        <v>7084096</v>
+        <v>7084114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132706135</v>
+        <v>132706116</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484208</v>
+        <v>484434</v>
       </c>
       <c r="R3" t="n">
-        <v>7084096</v>
+        <v>7084114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706116</v>
+        <v>132706135</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484434</v>
+        <v>484208</v>
       </c>
       <c r="R4" t="n">
-        <v>7084114</v>
+        <v>7084096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>132706106</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132706103</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>132706105</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>132706106</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132706103</v>
       </c>
       <c r="B12" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>132706105</v>
       </c>
       <c r="B13" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132706138</v>
       </c>
       <c r="B2" t="n">
-        <v>89300</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132706116</v>
+        <v>132706123</v>
       </c>
       <c r="B3" t="n">
-        <v>92378</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484434</v>
+        <v>484246</v>
       </c>
       <c r="R3" t="n">
-        <v>7084114</v>
+        <v>7084115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706135</v>
+        <v>132706099</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484208</v>
+        <v>484145</v>
       </c>
       <c r="R4" t="n">
-        <v>7084096</v>
+        <v>7084092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132706123</v>
+        <v>132706116</v>
       </c>
       <c r="B5" t="n">
-        <v>91914</v>
+        <v>92406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484246</v>
+        <v>484434</v>
       </c>
       <c r="R5" t="n">
-        <v>7084115</v>
+        <v>7084114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132706136</v>
+        <v>132706134</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484071</v>
+        <v>484488</v>
       </c>
       <c r="R6" t="n">
-        <v>7084084</v>
+        <v>7084185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132706099</v>
+        <v>132706135</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484145</v>
+        <v>484208</v>
       </c>
       <c r="R7" t="n">
-        <v>7084092</v>
+        <v>7084096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706115</v>
+        <v>132706136</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484521</v>
+        <v>484071</v>
       </c>
       <c r="R8" t="n">
-        <v>7084338</v>
+        <v>7084084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,53 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706104</v>
+        <v>132706137</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tuvattnet N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484193</v>
+        <v>484015</v>
       </c>
       <c r="R9" t="n">
-        <v>7084097</v>
+        <v>7084072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett ganska färskt troligt bohål,av tretåig hackspett, ca  3,5 m upp i tajgagrantickerötad gran. Även 2 äldre bohål av tretåig hackspett, på ca 1,2 respektive 1,7 meters höjd i samma gran. Bra skyddad placering med omgivande kullar o små blötstråk.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132706134</v>
+        <v>132706115</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1514,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484488</v>
+        <v>484521</v>
       </c>
       <c r="R10" t="n">
-        <v>7084185</v>
+        <v>7084338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132706106</v>
+        <v>117455593</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,14 +1599,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tuvattnet N, Jmt</t>
+          <t>Tuvattnet N NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484074</v>
+        <v>483946</v>
       </c>
       <c r="R11" t="n">
-        <v>7084107</v>
+        <v>7084187</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,17 +1633,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706105</v>
+        <v>132706104</v>
       </c>
       <c r="B13" t="n">
         <v>57975</v>
@@ -1809,16 +1801,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tuvattnet N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484399</v>
+        <v>484193</v>
       </c>
       <c r="R13" t="n">
-        <v>7084196</v>
+        <v>7084097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ett ganska färskt troligt bohål,av tretåig hackspett, ca  3,5 m upp i tajgagrantickerötad gran. Även 2 äldre bohål av tretåig hackspett, på ca 1,2 respektive 1,7 meters höjd i samma gran. Bra skyddad placering med omgivande kullar o små blötstråk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,6 +1879,210 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132706105</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tuvattnet N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>484399</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7084196</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132706106</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tuvattnet N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>484074</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7084107</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15025-2026 artfynd.xlsx
+++ b/artfynd/A 15025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706123</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706099</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706116</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706115</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706103</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706104</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,8 +2153,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132706106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>